--- a/حركات_الشركات_منظمة/البصريات/حركات_JFZ.xlsx
+++ b/حركات_الشركات_منظمة/البصريات/حركات_JFZ.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787009CE-4025-4ABD-BB4B-F4826268BD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="النظارات" state="visible" r:id="rId4"/>
+    <sheet name="النظارات" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="433">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -1310,35 +1314,31 @@
   </si>
   <si>
     <t>JFZ0128</t>
-  </si>
-  <si>
-    <t>JFZ2025</t>
-  </si>
-  <si>
-    <t>JFZ0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1709,9 +1709,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I142"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I131"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.69921875" customWidth="1"/>
     <col min="2" max="2" width="35.09765625" customWidth="1"/>
@@ -2363,7 +2363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>111</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>114</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>117</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>120</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>123</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>147</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>154</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>157</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>161</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>164</v>
       </c>
@@ -4346,96 +4346,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" t="s">
-        <v>433</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
-        <v>433</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" t="s">
-        <v>433</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
-        <v>433</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>433</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
-        <v>433</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
-        <v>433</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
-        <v>433</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" t="s">
-        <v>433</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
-        <v>433</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>433</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>